--- a/automotive_forms/037_roadside_assistance_check_in_form--automotive_forms.xlsx
+++ b/automotive_forms/037_roadside_assistance_check_in_form--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first name</t>
+          <t>First name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>vehicle_year</t>
+          <t>Vehicle year</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>vehicle_make</t>
+          <t>Vehicle make</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>vehicle_model</t>
+          <t>Vehicle model</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>vehicle_color</t>
+          <t>Vehicle color</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assistance_type</t>
+          <t>Assistance type</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assistance_location</t>
+          <t>Assistance location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Additional comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>assistance_date</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date of assistance</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>assistance_time</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Time of assistance</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>date_time</t>
+          <t>assistance_datetime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>date_and_time</t>
+          <t>Date and time of assistance</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vehicle_year</t>
+          <t>assistance_type_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>vehicle_year</t>
+          <t>Type of assistance</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vehicle_make</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vehicle_make</t>
+          <t>Location 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>vehicle_model</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vehicle_model</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>vehicle_color</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>vehicle_color</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assistance_type</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>assistance_type</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assistance_location</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>assistance_location</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>date_time</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>date_time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1182,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>location1</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>location1</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>location2</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>location2</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1216,19 +1055,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>location3</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>location3</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assistance_type_choices</t>
+          <t>assistance_type_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assistance_type_choices</t>
+          <t>assistance_type_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1101,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assistance_type_choices</t>
+          <t>assistance_type_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1273,57 +1112,6 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>Assistance with fuel delivery</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>assistance_location_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>location1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>location1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>assistance_location_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>location2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>location2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>assistance_location_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>location3</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>location3</t>
         </is>
       </c>
     </row>
